--- a/Methanol/Höchst_Methanol_1_DAC_Greenfield/Datenbank.xlsx
+++ b/Methanol/Höchst_Methanol_1_DAC_Greenfield/Datenbank.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Methanol_DAC_Greenfield_Höchst\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Höchst_Methanol_1_DAC_Greenfield\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0677BEA-8C71-4CDC-9C07-CCF2590B8950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03C3968-B53A-4A96-B156-6284C9EBDB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-6945" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
     <sheet name="Ergebnisse" sheetId="5" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="9.8999999999999999E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="364">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1285,6 +1285,12 @@
   </si>
   <si>
     <t>kg</t>
+  </si>
+  <si>
+    <t>Landesspezifischer Zinssatz</t>
+  </si>
+  <si>
+    <t>wacc_change</t>
   </si>
 </sst>
 </file>
@@ -1835,24 +1841,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G72"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G73"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="22" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="22" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" style="6" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="13.90625" style="6" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="6"/>
+    <col min="11" max="11" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.90625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>69</v>
       </c>
@@ -1873,7 +1879,7 @@
       </c>
       <c r="G1" s="22"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="31" t="s">
         <v>70</v>
       </c>
@@ -1893,7 +1899,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="32"/>
       <c r="B3" s="39"/>
       <c r="C3" s="6" t="s">
@@ -1909,7 +1915,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="32"/>
       <c r="B4" s="39"/>
       <c r="C4" s="6" t="s">
@@ -1925,7 +1931,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="32"/>
       <c r="B5" s="39"/>
       <c r="C5" s="6" t="s">
@@ -1941,7 +1947,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="32"/>
       <c r="B6" s="39"/>
       <c r="C6" s="6" t="s">
@@ -1957,7 +1963,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="32"/>
       <c r="B7" s="39"/>
       <c r="C7" s="6" t="s">
@@ -1973,7 +1979,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="32"/>
       <c r="B8" s="42" t="s">
         <v>228</v>
@@ -1991,7 +1997,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="32"/>
       <c r="B9" s="39"/>
       <c r="C9" s="6" t="s">
@@ -2007,7 +2013,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="32"/>
       <c r="B10" s="39"/>
       <c r="C10" s="6" t="s">
@@ -2023,7 +2029,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="32"/>
       <c r="B11" s="39"/>
       <c r="C11" s="6" t="s">
@@ -2039,7 +2045,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="32"/>
       <c r="B12" s="39"/>
       <c r="C12" s="6" t="s">
@@ -2055,7 +2061,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="32"/>
       <c r="B13" s="39"/>
       <c r="C13" s="6" t="s">
@@ -2071,7 +2077,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="32"/>
       <c r="B14" s="39"/>
       <c r="C14" s="6" t="s">
@@ -2087,7 +2093,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="32"/>
       <c r="B15" s="43"/>
       <c r="C15" s="14" t="s">
@@ -2103,7 +2109,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="32"/>
       <c r="B16" s="42" t="s">
         <v>284</v>
@@ -2121,7 +2127,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="32"/>
       <c r="B17" s="39"/>
       <c r="C17" s="6" t="s">
@@ -2137,7 +2143,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="32"/>
       <c r="B18" s="39"/>
       <c r="C18" s="6" t="s">
@@ -2153,7 +2159,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="32"/>
       <c r="B19" s="39"/>
       <c r="C19" s="6" t="s">
@@ -2169,7 +2175,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="32"/>
       <c r="B20" s="39"/>
       <c r="C20" s="6" t="s">
@@ -2185,7 +2191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="32"/>
       <c r="B21" s="43"/>
       <c r="C21" s="14" t="s">
@@ -2201,7 +2207,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="32"/>
       <c r="B22" s="35" t="s">
         <v>227</v>
@@ -2219,7 +2225,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="32"/>
       <c r="B23" s="35"/>
       <c r="C23" s="6" t="s">
@@ -2235,7 +2241,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="32"/>
       <c r="B24" s="35"/>
       <c r="C24" s="6" t="s">
@@ -2251,7 +2257,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="32"/>
       <c r="B25" s="35"/>
       <c r="C25" s="6" t="s">
@@ -2267,7 +2273,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="32"/>
       <c r="B26" s="35"/>
       <c r="C26" s="6" t="s">
@@ -2283,7 +2289,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="32"/>
       <c r="B27" s="35"/>
       <c r="C27" s="6" t="s">
@@ -2299,7 +2305,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="31" t="s">
         <v>71</v>
       </c>
@@ -2319,7 +2325,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="32"/>
       <c r="B29" s="35"/>
       <c r="C29" s="6" t="s">
@@ -2335,7 +2341,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="32"/>
       <c r="B30" s="35"/>
       <c r="C30" s="6" t="s">
@@ -2351,7 +2357,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="32"/>
       <c r="B31" s="35"/>
       <c r="C31" s="6" t="s">
@@ -2367,7 +2373,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="32"/>
       <c r="B32" s="35"/>
       <c r="C32" s="6" t="s">
@@ -2383,7 +2389,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="32"/>
       <c r="B33" s="35"/>
       <c r="C33" s="6" t="s">
@@ -2399,7 +2405,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="32"/>
       <c r="B34" s="35"/>
       <c r="C34" s="6" t="s">
@@ -2415,7 +2421,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="32"/>
       <c r="B35" s="36"/>
       <c r="C35" s="14" t="s">
@@ -2431,7 +2437,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="32"/>
       <c r="B36" s="37" t="s">
         <v>329</v>
@@ -2449,7 +2455,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="32"/>
       <c r="B37" s="35"/>
       <c r="C37" s="6" t="s">
@@ -2465,7 +2471,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="32"/>
       <c r="B38" s="35"/>
       <c r="C38" s="6" t="s">
@@ -2481,7 +2487,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="32"/>
       <c r="B39" s="35"/>
       <c r="C39" s="6" t="s">
@@ -2497,7 +2503,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="32"/>
       <c r="B40" s="35"/>
       <c r="C40" s="6" t="s">
@@ -2513,7 +2519,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="32"/>
       <c r="B41" s="35"/>
       <c r="C41" s="6" t="s">
@@ -2529,7 +2535,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="32"/>
       <c r="B42" s="35"/>
       <c r="C42" s="6" t="s">
@@ -2545,7 +2551,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="32"/>
       <c r="B43" s="35"/>
       <c r="C43" s="14" t="s">
@@ -2561,7 +2567,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="32"/>
       <c r="B44" s="37" t="s">
         <v>201</v>
@@ -2579,7 +2585,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="32"/>
       <c r="B45" s="39"/>
       <c r="C45" s="6" t="s">
@@ -2596,7 +2602,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="32"/>
       <c r="B46" s="39"/>
       <c r="C46" s="6" t="s">
@@ -2612,7 +2618,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="32"/>
       <c r="B47" s="39"/>
       <c r="C47" s="6" t="s">
@@ -2628,7 +2634,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="32"/>
       <c r="B48" s="39"/>
       <c r="C48" s="6" t="s">
@@ -2644,7 +2650,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="32"/>
       <c r="B49" s="39"/>
       <c r="C49" s="6" t="s">
@@ -2660,7 +2666,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="32"/>
       <c r="B50" s="39"/>
       <c r="C50" s="6" t="s">
@@ -2676,7 +2682,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="32"/>
       <c r="B51" s="39"/>
       <c r="C51" s="6" t="s">
@@ -2692,7 +2698,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="32"/>
       <c r="B52" s="39"/>
       <c r="C52" s="6" t="s">
@@ -2708,7 +2714,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="33"/>
       <c r="B53" s="40"/>
       <c r="C53" s="18" t="s">
@@ -2724,7 +2730,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="31" t="s">
         <v>72</v>
       </c>
@@ -2744,7 +2750,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="32"/>
       <c r="B55" s="37" t="s">
         <v>4</v>
@@ -2762,7 +2768,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="32"/>
       <c r="B56" s="35"/>
       <c r="C56" s="6" t="s">
@@ -2778,7 +2784,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="32"/>
       <c r="B57" s="35"/>
       <c r="C57" s="6" t="s">
@@ -2794,7 +2800,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="32"/>
       <c r="B58" s="35"/>
       <c r="C58" s="6" t="s">
@@ -2810,7 +2816,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="32"/>
       <c r="B59" s="35"/>
       <c r="C59" s="6" t="s">
@@ -2826,7 +2832,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="32"/>
       <c r="B60" s="35"/>
       <c r="C60" s="6" t="s">
@@ -2842,7 +2848,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="32"/>
       <c r="B61" s="36"/>
       <c r="C61" s="14" t="s">
@@ -2858,7 +2864,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="32"/>
       <c r="B62" s="37" t="s">
         <v>5</v>
@@ -2876,7 +2882,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="32"/>
       <c r="B63" s="35"/>
       <c r="C63" s="6" t="s">
@@ -2892,7 +2898,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="32"/>
       <c r="B64" s="35"/>
       <c r="C64" s="6" t="s">
@@ -2908,7 +2914,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="32"/>
       <c r="B65" s="35"/>
       <c r="C65" s="6" t="s">
@@ -2924,7 +2930,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="32"/>
       <c r="B66" s="35"/>
       <c r="C66" s="6" t="s">
@@ -2940,7 +2946,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="32"/>
       <c r="B67" s="35"/>
       <c r="C67" s="6" t="s">
@@ -2956,7 +2962,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="33"/>
       <c r="B68" s="38"/>
       <c r="C68" s="18" t="s">
@@ -2972,7 +2978,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="31" t="s">
         <v>76</v>
       </c>
@@ -2992,7 +2998,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="32"/>
       <c r="B70" s="22" t="s">
         <v>313</v>
@@ -3010,7 +3016,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="32"/>
       <c r="B71" s="28" t="s">
         <v>79</v>
@@ -3028,7 +3034,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="33"/>
       <c r="B72" s="4" t="s">
         <v>272</v>
@@ -3044,6 +3050,26 @@
       </c>
       <c r="F72" s="18" t="s">
         <v>286</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E73" s="11">
+        <v>0</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3071,18 +3097,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
   <dimension ref="A1:F141"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="37.5546875" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="6"/>
+    <col min="1" max="1" width="14.54296875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.81640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="46.08984375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="37.54296875" style="6" customWidth="1"/>
+    <col min="7" max="16384" width="11.54296875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>69</v>
       </c>
@@ -3102,7 +3128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="31" t="s">
         <v>70</v>
       </c>
@@ -3120,7 +3146,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="32"/>
       <c r="B3" s="39"/>
       <c r="C3" s="6" t="s">
@@ -3134,7 +3160,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="32"/>
       <c r="B4" s="39"/>
       <c r="C4" s="6" t="s">
@@ -3148,7 +3174,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="32"/>
       <c r="B5" s="39"/>
       <c r="C5" s="6" t="s">
@@ -3162,7 +3188,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="32"/>
       <c r="B6" s="39"/>
       <c r="C6" s="6" t="s">
@@ -3176,7 +3202,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="32"/>
       <c r="B7" s="39"/>
       <c r="C7" s="6" t="s">
@@ -3190,7 +3216,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="32"/>
       <c r="B8" s="39"/>
       <c r="C8" s="6" t="s">
@@ -3204,7 +3230,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="32"/>
       <c r="B9" s="39"/>
       <c r="C9" s="6" t="s">
@@ -3218,7 +3244,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="32"/>
       <c r="B10" s="39"/>
       <c r="C10" s="6" t="s">
@@ -3232,12 +3258,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="32"/>
       <c r="B11" s="39"/>
       <c r="E11" s="11"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="32"/>
       <c r="B12" s="42" t="s">
         <v>228</v>
@@ -3253,7 +3279,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="32"/>
       <c r="B13" s="39"/>
       <c r="C13" s="6" t="s">
@@ -3267,7 +3293,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="32"/>
       <c r="B14" s="39"/>
       <c r="C14" s="6" t="s">
@@ -3281,7 +3307,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="32"/>
       <c r="B15" s="39"/>
       <c r="C15" s="6" t="s">
@@ -3295,7 +3321,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="32"/>
       <c r="B16" s="39"/>
       <c r="C16" s="6" t="s">
@@ -3309,7 +3335,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="32"/>
       <c r="B17" s="39"/>
       <c r="C17" s="6" t="s">
@@ -3323,7 +3349,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="32"/>
       <c r="B18" s="39"/>
       <c r="C18" s="6" t="s">
@@ -3337,7 +3363,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="32"/>
       <c r="B19" s="39"/>
       <c r="C19" s="6" t="s">
@@ -3351,7 +3377,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="32"/>
       <c r="B20" s="39"/>
       <c r="C20" s="6" t="s">
@@ -3365,7 +3391,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="32"/>
       <c r="B21" s="39"/>
       <c r="C21" s="6" t="s">
@@ -3379,7 +3405,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="32"/>
       <c r="B22" s="43"/>
       <c r="C22" s="14"/>
@@ -3387,7 +3413,7 @@
       <c r="E22" s="15"/>
       <c r="F22" s="14"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="32"/>
       <c r="B23" s="42" t="s">
         <v>284</v>
@@ -3403,7 +3429,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="32"/>
       <c r="B24" s="39"/>
       <c r="C24" s="6" t="s">
@@ -3417,7 +3443,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="32"/>
       <c r="B25" s="39"/>
       <c r="C25" s="6" t="s">
@@ -3431,7 +3457,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="32"/>
       <c r="B26" s="39"/>
       <c r="C26" s="6" t="s">
@@ -3445,7 +3471,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="32"/>
       <c r="B27" s="39"/>
       <c r="C27" s="6" t="s">
@@ -3459,7 +3485,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="32"/>
       <c r="B28" s="39"/>
       <c r="C28" s="6" t="s">
@@ -3473,7 +3499,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="32"/>
       <c r="B29" s="39"/>
       <c r="C29" s="6" t="s">
@@ -3487,7 +3513,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="32"/>
       <c r="B30" s="39"/>
       <c r="C30" s="6" t="s">
@@ -3501,7 +3527,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="32"/>
       <c r="B31" s="39"/>
       <c r="C31" s="6" t="s">
@@ -3515,7 +3541,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="32"/>
       <c r="B32" s="43"/>
       <c r="C32" s="14"/>
@@ -3523,7 +3549,7 @@
       <c r="E32" s="15"/>
       <c r="F32" s="14"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="32"/>
       <c r="B33" s="35" t="s">
         <v>227</v>
@@ -3539,7 +3565,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="32"/>
       <c r="B34" s="35"/>
       <c r="C34" s="6" t="s">
@@ -3553,7 +3579,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="32"/>
       <c r="B35" s="35"/>
       <c r="C35" s="6" t="s">
@@ -3567,7 +3593,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="32"/>
       <c r="B36" s="35"/>
       <c r="C36" s="6" t="s">
@@ -3581,7 +3607,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="32"/>
       <c r="B37" s="35"/>
       <c r="C37" s="6" t="s">
@@ -3595,7 +3621,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="32"/>
       <c r="B38" s="35"/>
       <c r="C38" s="6" t="s">
@@ -3609,7 +3635,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="32"/>
       <c r="B39" s="35"/>
       <c r="C39" s="6" t="s">
@@ -3623,7 +3649,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="32"/>
       <c r="B40" s="35"/>
       <c r="C40" s="6" t="s">
@@ -3637,7 +3663,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="32"/>
       <c r="B41" s="35"/>
       <c r="C41" s="6" t="s">
@@ -3651,7 +3677,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="32"/>
       <c r="B42" s="35"/>
       <c r="C42" s="6" t="s">
@@ -3665,12 +3691,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="32"/>
       <c r="B43" s="35"/>
       <c r="E43" s="11"/>
     </row>
-    <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="31" t="s">
         <v>71</v>
       </c>
@@ -3688,7 +3714,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="32"/>
       <c r="B45" s="35"/>
       <c r="C45" s="6" t="s">
@@ -3702,7 +3728,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="32"/>
       <c r="B46" s="35"/>
       <c r="C46" s="6" t="s">
@@ -3716,7 +3742,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="32"/>
       <c r="B47" s="35"/>
       <c r="C47" s="6" t="s">
@@ -3730,7 +3756,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="32"/>
       <c r="B48" s="35"/>
       <c r="C48" s="6" t="s">
@@ -3744,7 +3770,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="32"/>
       <c r="B49" s="35"/>
       <c r="C49" s="6" t="s">
@@ -3758,7 +3784,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="32"/>
       <c r="B50" s="35"/>
       <c r="C50" s="6" t="s">
@@ -3772,7 +3798,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="32"/>
       <c r="B51" s="35"/>
       <c r="C51" s="6" t="s">
@@ -3786,7 +3812,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="32"/>
       <c r="B52" s="35"/>
       <c r="C52" s="6" t="s">
@@ -3800,7 +3826,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="32"/>
       <c r="B53" s="36"/>
       <c r="C53" s="14"/>
@@ -3808,7 +3834,7 @@
       <c r="E53" s="15"/>
       <c r="F53" s="14"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="32"/>
       <c r="B54" s="35" t="s">
         <v>329</v>
@@ -3824,7 +3850,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="32"/>
       <c r="B55" s="35"/>
       <c r="C55" s="6" t="s">
@@ -3838,7 +3864,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="32"/>
       <c r="B56" s="35"/>
       <c r="C56" s="6" t="s">
@@ -3852,7 +3878,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="32"/>
       <c r="B57" s="35"/>
       <c r="C57" s="6" t="s">
@@ -3866,7 +3892,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="32"/>
       <c r="B58" s="35"/>
       <c r="C58" s="6" t="s">
@@ -3880,7 +3906,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="32"/>
       <c r="B59" s="35"/>
       <c r="C59" s="6" t="s">
@@ -3894,7 +3920,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="32"/>
       <c r="B60" s="35"/>
       <c r="C60" s="6" t="s">
@@ -3908,7 +3934,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="32"/>
       <c r="B61" s="35"/>
       <c r="C61" s="6" t="s">
@@ -3922,7 +3948,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="32"/>
       <c r="B62" s="35"/>
       <c r="C62" s="6" t="s">
@@ -3936,12 +3962,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="32"/>
       <c r="B63" s="36"/>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="32"/>
       <c r="B64" s="37" t="s">
         <v>6</v>
@@ -3957,7 +3983,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="32"/>
       <c r="B65" s="35"/>
       <c r="C65" s="6" t="s">
@@ -3971,7 +3997,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="32"/>
       <c r="B66" s="39"/>
       <c r="C66" s="6" t="s">
@@ -3985,7 +4011,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="32"/>
       <c r="B67" s="39"/>
       <c r="C67" s="6" t="s">
@@ -3999,7 +4025,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="32"/>
       <c r="B68" s="39"/>
       <c r="C68" s="6" t="s">
@@ -4013,7 +4039,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="32"/>
       <c r="B69" s="39"/>
       <c r="C69" s="6" t="s">
@@ -4027,7 +4053,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="32"/>
       <c r="B70" s="39"/>
       <c r="C70" s="6" t="s">
@@ -4041,7 +4067,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="32"/>
       <c r="B71" s="39"/>
       <c r="C71" s="6" t="s">
@@ -4055,7 +4081,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="32"/>
       <c r="B72" s="39"/>
       <c r="C72" s="6" t="s">
@@ -4069,7 +4095,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="32"/>
       <c r="B73" s="39"/>
       <c r="C73" s="6" t="s">
@@ -4083,7 +4109,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="32"/>
       <c r="B74" s="39"/>
       <c r="C74" s="6" t="s">
@@ -4097,7 +4123,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="33"/>
       <c r="B75" s="40"/>
       <c r="C75" s="18"/>
@@ -4105,7 +4131,7 @@
       <c r="E75" s="19"/>
       <c r="F75" s="18"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="31" t="s">
         <v>72</v>
       </c>
@@ -4123,7 +4149,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="32"/>
       <c r="B77" s="39"/>
       <c r="C77" s="6" t="s">
@@ -4137,12 +4163,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="32"/>
       <c r="B78" s="43"/>
       <c r="E78" s="9"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="32"/>
       <c r="B79" s="37" t="s">
         <v>4</v>
@@ -4158,7 +4184,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="32"/>
       <c r="B80" s="35"/>
       <c r="C80" s="6" t="s">
@@ -4172,7 +4198,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="32"/>
       <c r="B81" s="35"/>
       <c r="C81" s="6" t="s">
@@ -4186,7 +4212,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="32"/>
       <c r="B82" s="35"/>
       <c r="C82" s="6" t="s">
@@ -4200,7 +4226,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="32"/>
       <c r="B83" s="35"/>
       <c r="C83" s="6" t="s">
@@ -4214,7 +4240,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="32"/>
       <c r="B84" s="35"/>
       <c r="C84" s="6" t="s">
@@ -4228,7 +4254,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="32"/>
       <c r="B85" s="35"/>
       <c r="C85" s="6" t="s">
@@ -4242,7 +4268,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="32"/>
       <c r="B86" s="35"/>
       <c r="C86" s="6" t="s">
@@ -4256,7 +4282,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="32"/>
       <c r="B87" s="35"/>
       <c r="C87" s="6" t="s">
@@ -4270,11 +4296,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="32"/>
       <c r="B88" s="36"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="32"/>
       <c r="B89" s="37" t="s">
         <v>5</v>
@@ -4290,7 +4316,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="32"/>
       <c r="B90" s="35"/>
       <c r="C90" s="6" t="s">
@@ -4304,7 +4330,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="32"/>
       <c r="B91" s="35"/>
       <c r="C91" s="6" t="s">
@@ -4318,7 +4344,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="32"/>
       <c r="B92" s="35"/>
       <c r="C92" s="6" t="s">
@@ -4332,7 +4358,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="32"/>
       <c r="B93" s="35"/>
       <c r="C93" s="6" t="s">
@@ -4346,7 +4372,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="32"/>
       <c r="B94" s="35"/>
       <c r="C94" s="6" t="s">
@@ -4360,7 +4386,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="32"/>
       <c r="B95" s="35"/>
       <c r="C95" s="6" t="s">
@@ -4374,7 +4400,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="32"/>
       <c r="B96" s="35"/>
       <c r="C96" s="6" t="s">
@@ -4388,7 +4414,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="32"/>
       <c r="B97" s="35"/>
       <c r="C97" s="6" t="s">
@@ -4402,11 +4428,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="33"/>
       <c r="B98" s="38"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="31" t="s">
         <v>76</v>
       </c>
@@ -4424,7 +4450,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="32"/>
       <c r="B100" s="39"/>
       <c r="C100" s="6" t="s">
@@ -4438,7 +4464,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="32"/>
       <c r="B101" s="43"/>
       <c r="C101" s="14"/>
@@ -4446,7 +4472,7 @@
       <c r="E101" s="15"/>
       <c r="F101" s="14"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="32"/>
       <c r="B102" s="42" t="s">
         <v>317</v>
@@ -4462,7 +4488,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="32"/>
       <c r="B103" s="39"/>
       <c r="C103" s="6" t="s">
@@ -4476,12 +4502,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="32"/>
       <c r="B104" s="43"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="32"/>
       <c r="B105" s="42" t="s">
         <v>79</v>
@@ -4497,7 +4523,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="32"/>
       <c r="B106" s="39"/>
       <c r="C106" s="6" t="s">
@@ -4511,7 +4537,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="32"/>
       <c r="B107" s="43"/>
       <c r="C107" s="14"/>
@@ -4519,7 +4545,7 @@
       <c r="E107" s="15"/>
       <c r="F107" s="14"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="32"/>
       <c r="B108" s="42" t="s">
         <v>272</v>
@@ -4535,7 +4561,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="32"/>
       <c r="B109" s="39"/>
       <c r="C109" s="6" t="s">
@@ -4549,7 +4575,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="33"/>
       <c r="B110" s="40"/>
       <c r="C110" s="18"/>
@@ -4557,7 +4583,7 @@
       <c r="E110" s="19"/>
       <c r="F110" s="18"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="31" t="s">
         <v>163</v>
       </c>
@@ -4575,7 +4601,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="32"/>
       <c r="B112" s="39"/>
       <c r="C112" s="6" t="s">
@@ -4588,7 +4614,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="32"/>
       <c r="B113" s="43"/>
       <c r="C113" s="14"/>
@@ -4596,7 +4622,7 @@
       <c r="E113" s="14"/>
       <c r="F113" s="14"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="32"/>
       <c r="B114" s="42" t="s">
         <v>183</v>
@@ -4611,7 +4637,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="32"/>
       <c r="B115" s="39"/>
       <c r="C115" s="6" t="s">
@@ -4624,7 +4650,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="32"/>
       <c r="B116" s="39"/>
       <c r="C116" s="6" t="s">
@@ -4637,7 +4663,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="32"/>
       <c r="B117" s="39"/>
       <c r="C117" s="6" t="s">
@@ -4650,7 +4676,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="32"/>
       <c r="B118" s="39"/>
       <c r="C118" s="6" t="s">
@@ -4663,7 +4689,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="32"/>
       <c r="B119" s="39"/>
       <c r="C119" s="6" t="s">
@@ -4676,11 +4702,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="32"/>
       <c r="B120" s="39"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="32"/>
       <c r="B121" s="42" t="s">
         <v>206</v>
@@ -4696,7 +4722,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="32"/>
       <c r="B122" s="39"/>
       <c r="C122" s="6" t="s">
@@ -4709,7 +4735,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="32"/>
       <c r="B123" s="39"/>
       <c r="C123" s="6" t="s">
@@ -4722,7 +4748,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="32"/>
       <c r="B124" s="39"/>
       <c r="C124" s="6" t="s">
@@ -4735,7 +4761,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="32"/>
       <c r="B125" s="39"/>
       <c r="C125" s="6" t="s">
@@ -4748,7 +4774,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="32"/>
       <c r="B126" s="39"/>
       <c r="C126" s="6" t="s">
@@ -4761,7 +4787,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="32"/>
       <c r="B127" s="39"/>
       <c r="C127" s="6" t="s">
@@ -4774,7 +4800,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="32"/>
       <c r="B128" s="39"/>
       <c r="C128" s="6" t="s">
@@ -4787,7 +4813,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="32"/>
       <c r="B129" s="39"/>
       <c r="C129" s="6" t="s">
@@ -4800,7 +4826,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="32"/>
       <c r="B130" s="39"/>
       <c r="C130" s="6" t="s">
@@ -4813,7 +4839,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="32"/>
       <c r="B131" s="39"/>
       <c r="C131" s="6" t="s">
@@ -4826,7 +4852,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="32"/>
       <c r="B132" s="39"/>
       <c r="C132" s="6" t="s">
@@ -4839,11 +4865,11 @@
         <v>213</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="32"/>
       <c r="B133" s="39"/>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="32"/>
       <c r="B134" s="42" t="s">
         <v>222</v>
@@ -4859,7 +4885,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="32"/>
       <c r="B135" s="39"/>
       <c r="C135" s="6" t="s">
@@ -4872,7 +4898,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="32"/>
       <c r="B136" s="39"/>
       <c r="C136" s="6" t="s">
@@ -4885,7 +4911,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="32"/>
       <c r="B137" s="39"/>
       <c r="C137" s="6" t="s">
@@ -4898,7 +4924,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="32"/>
       <c r="B138" s="39"/>
       <c r="C138" s="6" t="s">
@@ -4911,11 +4937,11 @@
         <v>213</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="32"/>
       <c r="B139" s="43"/>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="32"/>
       <c r="B140" s="42" t="s">
         <v>354</v>
@@ -4931,7 +4957,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="32"/>
       <c r="B141" s="39"/>
       <c r="C141" s="6" t="s">
@@ -4946,6 +4972,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="A76:A98"/>
+    <mergeCell ref="B79:B88"/>
+    <mergeCell ref="B89:B98"/>
+    <mergeCell ref="A99:A110"/>
+    <mergeCell ref="B105:B107"/>
+    <mergeCell ref="B99:B101"/>
+    <mergeCell ref="B102:B104"/>
     <mergeCell ref="B140:B141"/>
     <mergeCell ref="A111:A141"/>
     <mergeCell ref="B134:B139"/>
@@ -4962,14 +4996,6 @@
     <mergeCell ref="B76:B78"/>
     <mergeCell ref="B114:B120"/>
     <mergeCell ref="B121:B133"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="A76:A98"/>
-    <mergeCell ref="B79:B88"/>
-    <mergeCell ref="B89:B98"/>
-    <mergeCell ref="A99:A110"/>
-    <mergeCell ref="B105:B107"/>
-    <mergeCell ref="B99:B101"/>
-    <mergeCell ref="B102:B104"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Höchst_Methanol_1_DAC_Greenfield/Datenbank.xlsx
+++ b/Methanol/Höchst_Methanol_1_DAC_Greenfield/Datenbank.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03C3968-B53A-4A96-B156-6284C9EBDB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-6945" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-6885" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -4972,14 +4972,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="A76:A98"/>
-    <mergeCell ref="B79:B88"/>
-    <mergeCell ref="B89:B98"/>
-    <mergeCell ref="A99:A110"/>
-    <mergeCell ref="B105:B107"/>
-    <mergeCell ref="B99:B101"/>
-    <mergeCell ref="B102:B104"/>
     <mergeCell ref="B140:B141"/>
     <mergeCell ref="A111:A141"/>
     <mergeCell ref="B134:B139"/>
@@ -4996,6 +4988,14 @@
     <mergeCell ref="B76:B78"/>
     <mergeCell ref="B114:B120"/>
     <mergeCell ref="B121:B133"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="A76:A98"/>
+    <mergeCell ref="B79:B88"/>
+    <mergeCell ref="B89:B98"/>
+    <mergeCell ref="A99:A110"/>
+    <mergeCell ref="B105:B107"/>
+    <mergeCell ref="B99:B101"/>
+    <mergeCell ref="B102:B104"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
